--- a/nriss-patch-1/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:55:04+00:00</t>
+    <t>2026-02-24T08:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1)}fr-core-3:If identityReliability status = 'VALI', then the municipality of birth COG code cannot be 99999 because this code cannot be sent by the INSI online service. {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies extension('http://hl7.org/fhir/StructureDefinition/patient-birthPlace').value.extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code').value.code != '99999')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST] or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8' and use = 'official' and type.coding.exists(code = 'INS-NIR')).exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10' and use = 'official').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11' and use = 'official').exists())}fr-core-2:If identityReliability status = 'VALI', then only one identifier of type official SHALL be present {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies (identifier.where(use = 'official').count() = 1)}fr-core-3:If identityReliability status = 'VALI', then the municipality of birth COG code cannot be 99999 because this code cannot be sent by the INSI online service. {(extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension('identityStatus').value.exists(code = 'VALI')) implies extension('http://hl7.org/fhir/StructureDefinition/patient-birthPlace').value.extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address-insee-code').value.code != '99999'}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>

--- a/nriss-patch-1/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T10:29:07+00:00</t>
+    <t>2026-06-05T13:13:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -958,7 +958,7 @@
     <t>FR Core Address Insee Code Extension</t>
   </si>
   <si>
-    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale. Dans le cas d'une ville étrangère, le code département devient "99" et le code commune est renseigné avec le code pays.
+    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale. Dans le cas d'une ville étrangère, le code département devient "99" et le code commune est renseigné avec le code pays. Pour plus de détails, consultez le référentiel national d'identitovigilance (RNIV).
 This extension adds the insee code (5 digits) to the address. In the case of a foreign city, the department code becomes "99", and the municipality code is populated with the country code.</t>
   </si>
   <si>
